--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9E12E3-8774-4C89-AD56-3F4370CA3FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61BBD5D-BD97-424A-B2CB-796D194E6FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="86">
   <si>
     <t>category</t>
   </si>
@@ -225,15 +225,6 @@
     <t>2040 dynamic scale</t>
   </si>
   <si>
-    <t>dynamic_scale_factor</t>
-  </si>
-  <si>
-    <t>2030_dynamic_scale_factor</t>
-  </si>
-  <si>
-    <t>2040_dynamic_scale_factor</t>
-  </si>
-  <si>
     <t>markey</t>
   </si>
   <si>
@@ -280,6 +271,48 @@
   </si>
   <si>
     <t>night_flat_ratio_2040</t>
+  </si>
+  <si>
+    <t>dynamic_tariff_scale</t>
+  </si>
+  <si>
+    <t>dynamic_tariff_scale_2040</t>
+  </si>
+  <si>
+    <t>dynamic_tariff_scale_2030</t>
+  </si>
+  <si>
+    <t>2015 standing charge</t>
+  </si>
+  <si>
+    <t>standing_charge_2015</t>
+  </si>
+  <si>
+    <t>euros</t>
+  </si>
+  <si>
+    <t>standing_charge_2022</t>
+  </si>
+  <si>
+    <t>standing_charge_2025</t>
+  </si>
+  <si>
+    <t>standing_charge_2030</t>
+  </si>
+  <si>
+    <t>standing_charge_2040</t>
+  </si>
+  <si>
+    <t>2022 standing charge</t>
+  </si>
+  <si>
+    <t>2025 standing charge</t>
+  </si>
+  <si>
+    <t>2030standing charge</t>
+  </si>
+  <si>
+    <t>2040 standing charge</t>
   </si>
 </sst>
 </file>
@@ -787,7 +820,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -858,7 +891,7 @@
         <v>39</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D4">
         <v>0.4</v>
@@ -876,7 +909,7 @@
         <v>40</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D5">
         <v>0.4</v>
@@ -888,19 +921,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D6">
         <v>0.52500000000000002</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F6" s="1"/>
     </row>
@@ -912,13 +945,13 @@
         <v>45</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D7">
         <v>0.52500000000000002</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F7" s="1"/>
     </row>
@@ -930,13 +963,13 @@
         <v>46</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D8">
         <v>0.52500000000000002</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F8" s="1"/>
     </row>
@@ -945,16 +978,16 @@
         <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D9">
-        <v>1.0669999999999999</v>
+        <v>1.0880000000000001</v>
       </c>
       <c r="E9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1"/>
     </row>
@@ -966,13 +999,13 @@
         <v>47</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D10">
-        <v>1.0669999999999999</v>
+        <v>1.0880000000000001</v>
       </c>
       <c r="E10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F10" s="1"/>
     </row>
@@ -984,13 +1017,13 @@
         <v>48</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D11">
-        <v>1.0669999999999999</v>
+        <v>1.0880000000000001</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F11" s="1"/>
     </row>
@@ -999,16 +1032,16 @@
         <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D12">
-        <v>1.0880000000000001</v>
+        <v>1.0660000000000001</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F12" s="1"/>
     </row>
@@ -1023,10 +1056,10 @@
         <v>51</v>
       </c>
       <c r="D13">
-        <v>1.0880000000000001</v>
+        <v>1.0660000000000001</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F13" s="1"/>
     </row>
@@ -1041,10 +1074,10 @@
         <v>52</v>
       </c>
       <c r="D14">
-        <v>1.0880000000000001</v>
+        <v>1.0660000000000001</v>
       </c>
       <c r="E14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F14" s="1"/>
     </row>
@@ -1056,13 +1089,13 @@
         <v>53</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D15">
         <v>3.1</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F15" s="1"/>
     </row>
@@ -1074,13 +1107,13 @@
         <v>54</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="D16">
         <v>3.1</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F16" s="1"/>
     </row>
@@ -1092,67 +1125,145 @@
         <v>55</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="D17">
         <v>3.1</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F17" s="1"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>14</v>
+        <v>75</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="D18">
-        <v>0.594322503</v>
+        <v>130</v>
       </c>
       <c r="E18" t="s">
-        <v>15</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="F18" s="1"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>8</v>
+        <v>82</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D19">
-        <v>4.8274562E-2</v>
-      </c>
-      <c r="E19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F19" s="1"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20">
+        <v>265</v>
+      </c>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21">
+        <v>320</v>
+      </c>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22">
+        <v>350</v>
+      </c>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>7</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23">
+        <v>0.594322503</v>
+      </c>
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24">
+        <v>4.8274562E-2</v>
+      </c>
+      <c r="E24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D20">
+      <c r="D25">
         <v>0.03</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E25" t="s">
         <v>18</v>
       </c>
     </row>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61BBD5D-BD97-424A-B2CB-796D194E6FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989D9BBD-DEA7-415A-ABC8-D59A854C0990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="90">
   <si>
     <t>category</t>
   </si>
@@ -313,6 +313,18 @@
   </si>
   <si>
     <t>2040 standing charge</t>
+  </si>
+  <si>
+    <t>transform scale (in asinh)</t>
+  </si>
+  <si>
+    <t>euro/kWh</t>
+  </si>
+  <si>
+    <t>s.</t>
+  </si>
+  <si>
+    <t>handling negative prices</t>
   </si>
 </sst>
 </file>
@@ -820,7 +832,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -1267,6 +1279,26 @@
         <v>18</v>
       </c>
     </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989D9BBD-DEA7-415A-ABC8-D59A854C0990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5160988-B94B-4C14-90C5-A6FCA9804B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="124">
   <si>
     <t>category</t>
   </si>
@@ -326,11 +326,116 @@
   <si>
     <t>handling negative prices</t>
   </si>
+  <si>
+    <t>technical</t>
+  </si>
+  <si>
+    <t>minimum household hourly flexibility</t>
+  </si>
+  <si>
+    <t>maximum household hourly flexibility</t>
+  </si>
+  <si>
+    <t>min_flex</t>
+  </si>
+  <si>
+    <t>max_flex</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>hourly MAD assuming 2026 dynamic prices and LP1 load</t>
+  </si>
+  <si>
+    <t>max risk aversion</t>
+  </si>
+  <si>
+    <t>theta.</t>
+  </si>
+  <si>
+    <t>dynamic price cap scale</t>
+  </si>
+  <si>
+    <t>dynamic_price_cap_scale</t>
+  </si>
+  <si>
+    <t>the current cap is dynamic_price_cap_scale*current flat price</t>
+  </si>
+  <si>
+    <t>night network charge</t>
+  </si>
+  <si>
+    <t>peak network charge</t>
+  </si>
+  <si>
+    <t>polixy</t>
+  </si>
+  <si>
+    <t>vat rate electricity</t>
+  </si>
+  <si>
+    <t>vat_rate</t>
+  </si>
+  <si>
+    <t>day network charge</t>
+  </si>
+  <si>
+    <t>day_network_charge_2020</t>
+  </si>
+  <si>
+    <t>night_network_charge_2020</t>
+  </si>
+  <si>
+    <t>peak_network_charge_2020</t>
+  </si>
+  <si>
+    <t>day_network_charge_2030</t>
+  </si>
+  <si>
+    <t>night_network_charge_2030</t>
+  </si>
+  <si>
+    <t>peak_network_charge_2030</t>
+  </si>
+  <si>
+    <t>regulated grid charges+supplier uplift (costs, margin)</t>
+  </si>
+  <si>
+    <t>15% below 2026 values</t>
+  </si>
+  <si>
+    <t>10% above 2026 values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30% above </t>
+  </si>
+  <si>
+    <t>day_network_charge_2026</t>
+  </si>
+  <si>
+    <t>night_network_charge_2026</t>
+  </si>
+  <si>
+    <t>peak_network_charge_2026</t>
+  </si>
+  <si>
+    <t>day_network_charge_2040</t>
+  </si>
+  <si>
+    <t>night_network_charge_2040</t>
+  </si>
+  <si>
+    <t>peak_network_charge_2040</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -393,12 +498,30 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -407,7 +530,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -424,6 +547,13 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="2" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -832,7 +962,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -897,253 +1027,249 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="D4">
-        <v>0.4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="1"/>
+        <v>0.09</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5">
-        <v>0.4</v>
+      <c r="A5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.16838500000000001</v>
       </c>
       <c r="E5" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="F5" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6">
-        <v>0.52500000000000002</v>
+      <c r="A6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="8">
+        <v>7.2419999999999998E-2</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="1"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7">
-        <v>0.52500000000000002</v>
+      <c r="A7" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.19167500000000001</v>
       </c>
       <c r="E7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="1"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>71</v>
+      <c r="A8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="D8">
-        <v>0.52500000000000002</v>
+        <v>0.1981</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>67</v>
+      <c r="A9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="D9">
-        <v>1.0880000000000001</v>
+        <v>8.5199999999999998E-2</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="1"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>68</v>
+      <c r="A10" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>120</v>
       </c>
       <c r="D10">
-        <v>1.0880000000000001</v>
+        <v>0.22550000000000001</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="1"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11">
-        <v>1.0880000000000001</v>
+      <c r="A11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0.21791000000000002</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12">
-        <v>1.0660000000000001</v>
+      <c r="A12" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="8">
+        <v>9.3720000000000012E-2</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="1"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13">
-        <v>1.0660000000000001</v>
+      <c r="A13" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.24805000000000002</v>
       </c>
       <c r="E13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="1"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14">
-        <v>1.0660000000000001</v>
+      <c r="A14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0.25752999999999998</v>
       </c>
       <c r="E14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="F14" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15">
-        <v>3.1</v>
+      <c r="A15" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0.11076</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" s="1"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16">
-        <v>3.1</v>
+      <c r="A16" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.29315000000000002</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" s="1"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D17">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="E17" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="F17" s="1"/>
     </row>
@@ -1152,31 +1278,34 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D18">
-        <v>130</v>
+        <v>0.4</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="F18" s="1"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D19">
-        <v>215</v>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E19" t="s">
+        <v>65</v>
       </c>
       <c r="F19" s="1"/>
     </row>
@@ -1185,13 +1314,16 @@
         <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D20">
-        <v>265</v>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E20" t="s">
+        <v>65</v>
       </c>
       <c r="F20" s="1"/>
     </row>
@@ -1200,13 +1332,16 @@
         <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D21">
-        <v>320</v>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E21" t="s">
+        <v>65</v>
       </c>
       <c r="F21" s="1"/>
     </row>
@@ -1215,88 +1350,387 @@
         <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D22">
-        <v>350</v>
+        <v>1.0880000000000001</v>
+      </c>
+      <c r="E22" t="s">
+        <v>65</v>
       </c>
       <c r="F22" s="1"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>14</v>
+        <v>47</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="D23">
-        <v>0.594322503</v>
+        <v>1.0880000000000001</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="F23" s="1"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>8</v>
+        <v>48</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="D24">
-        <v>4.8274562E-2</v>
+        <v>1.0880000000000001</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="F24" s="1"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>17</v>
+        <v>59</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="D25">
-        <v>0.03</v>
+        <v>1.0660000000000001</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="F25" s="1"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26">
+        <v>1.0660000000000001</v>
+      </c>
+      <c r="E26" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27">
+        <v>1.0660000000000001</v>
+      </c>
+      <c r="E27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28">
+        <v>3.1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29">
+        <v>3.1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30">
+        <v>3.1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>65</v>
+      </c>
+      <c r="F31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32">
+        <v>130</v>
+      </c>
+      <c r="E32" t="s">
+        <v>77</v>
+      </c>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33">
+        <v>215</v>
+      </c>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34">
+        <v>265</v>
+      </c>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35">
+        <v>320</v>
+      </c>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36">
+        <v>350</v>
+      </c>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38">
+        <v>30</v>
+      </c>
+      <c r="E38" t="s">
+        <v>95</v>
+      </c>
+      <c r="F38" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>7</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39">
+        <v>0.594322503</v>
+      </c>
+      <c r="E39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40">
+        <v>4.8274562E-2</v>
+      </c>
+      <c r="E40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41">
+        <v>0.03</v>
+      </c>
+      <c r="E41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D26">
+      <c r="D42">
         <v>10</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E42" t="s">
         <v>87</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F42" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5160988-B94B-4C14-90C5-A6FCA9804B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE3A243-80F5-44A1-8423-2282262088E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="106">
   <si>
     <t>category</t>
   </si>
@@ -66,9 +66,6 @@
     <t>p.</t>
   </si>
   <si>
-    <t>financial utility scale factor</t>
-  </si>
-  <si>
     <t>short description</t>
   </si>
   <si>
@@ -154,12 +151,6 @@
   </si>
   <si>
     <t>market</t>
-  </si>
-  <si>
-    <t>2030 flat electricity price</t>
-  </si>
-  <si>
-    <t>2040 flat electricity price</t>
   </si>
   <si>
     <r>
@@ -192,96 +183,15 @@
     <t>effective date for now (smart meter rollout)</t>
   </si>
   <si>
-    <t>2030 night day ratio</t>
-  </si>
-  <si>
-    <t>2040 night day ratio</t>
-  </si>
-  <si>
-    <t>2030 peak premium</t>
-  </si>
-  <si>
-    <t>2040 peak premium</t>
-  </si>
-  <si>
-    <t>2030 day to flat ratio</t>
-  </si>
-  <si>
-    <t>2040 day to flat ratio</t>
-  </si>
-  <si>
-    <t>day_flat_ratio_2030</t>
-  </si>
-  <si>
-    <t>day_flat_ratio_2040</t>
-  </si>
-  <si>
-    <t>2026 dynamic scale</t>
-  </si>
-  <si>
-    <t>2030 dynamic scale</t>
-  </si>
-  <si>
-    <t>2040 dynamic scale</t>
-  </si>
-  <si>
-    <t>markey</t>
-  </si>
-  <si>
-    <t>night to day priceratio</t>
-  </si>
-  <si>
-    <t>peak premium over day rate</t>
-  </si>
-  <si>
-    <t>day to flat rate ration</t>
-  </si>
-  <si>
-    <t>day_flat_ratio</t>
-  </si>
-  <si>
     <t>inertia param</t>
   </si>
   <si>
     <t>heterogeneous</t>
   </si>
   <si>
-    <t>flat_tariff_2030</t>
-  </si>
-  <si>
-    <t>flat_tariff_2040</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>night_flat_ratio</t>
-  </si>
-  <si>
-    <t>peak_flat_ratio</t>
-  </si>
-  <si>
-    <t>peak_flat_ratio_2030</t>
-  </si>
-  <si>
-    <t>peak_flat_ratio_2040</t>
-  </si>
-  <si>
-    <t>night_flat_ratio_2030</t>
-  </si>
-  <si>
-    <t>night_flat_ratio_2040</t>
-  </si>
-  <si>
-    <t>dynamic_tariff_scale</t>
-  </si>
-  <si>
-    <t>dynamic_tariff_scale_2040</t>
-  </si>
-  <si>
-    <t>dynamic_tariff_scale_2030</t>
-  </si>
-  <si>
     <t>2015 standing charge</t>
   </si>
   <si>
@@ -345,9 +255,6 @@
     <t>%</t>
   </si>
   <si>
-    <t>hourly MAD assuming 2026 dynamic prices and LP1 load</t>
-  </si>
-  <si>
     <t>max risk aversion</t>
   </si>
   <si>
@@ -369,15 +276,6 @@
     <t>peak network charge</t>
   </si>
   <si>
-    <t>polixy</t>
-  </si>
-  <si>
-    <t>vat rate electricity</t>
-  </si>
-  <si>
-    <t>vat_rate</t>
-  </si>
-  <si>
     <t>day network charge</t>
   </si>
   <si>
@@ -427,6 +325,54 @@
   </si>
   <si>
     <t>peak_network_charge_2040</t>
+  </si>
+  <si>
+    <t>2030 sem price</t>
+  </si>
+  <si>
+    <t>2040 sem price</t>
+  </si>
+  <si>
+    <t>mean wholesale price</t>
+  </si>
+  <si>
+    <t>sem_price_2030</t>
+  </si>
+  <si>
+    <t>sem_price_2040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vat rate electricity pre </t>
+  </si>
+  <si>
+    <t>vat rate electricity post</t>
+  </si>
+  <si>
+    <t>old_vat_rate</t>
+  </si>
+  <si>
+    <t>new_vat_rate</t>
+  </si>
+  <si>
+    <t>vat rate post 2030</t>
+  </si>
+  <si>
+    <t>post_2030_vat_rate</t>
+  </si>
+  <si>
+    <t>maximum import capacity</t>
+  </si>
+  <si>
+    <t>mic</t>
+  </si>
+  <si>
+    <t>12kVA or 12kWh</t>
+  </si>
+  <si>
+    <t>social factor</t>
+  </si>
+  <si>
+    <t>hourly MAE assuming 2026 dynamic prices and LP1 load</t>
   </si>
 </sst>
 </file>
@@ -434,7 +380,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -530,7 +476,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -547,10 +493,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="2" applyBorder="1"/>
@@ -882,77 +827,77 @@
   <sheetData>
     <row r="1" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="C5" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>26</v>
-      </c>
       <c r="C6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +907,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -995,13 +940,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="D2">
         <v>2026.5</v>
@@ -1010,726 +955,558 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>2021</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D4">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5">
         <v>0.09</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7">
+        <v>0.15</v>
+      </c>
+      <c r="E7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="8">
+      <c r="F7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8">
+        <v>0.2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="8">
         <v>0.16838500000000001</v>
       </c>
-      <c r="E5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="E9" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="8">
+      <c r="F9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="8">
         <v>7.2419999999999998E-2</v>
       </c>
-      <c r="E6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
+      <c r="E10" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="8">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="8">
         <v>0.19167500000000001</v>
       </c>
-      <c r="E7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="E11" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12">
         <v>0.1981</v>
       </c>
-      <c r="E8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="E12" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9">
+      <c r="F12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13">
         <v>8.5199999999999998E-2</v>
       </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="E13" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D10">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14">
         <v>0.22550000000000001</v>
       </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="E14" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" s="8">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="8">
         <v>0.21791000000000002</v>
       </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="E15" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="8">
+      <c r="F15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="8">
         <v>9.3720000000000012E-2</v>
       </c>
-      <c r="E12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
+      <c r="E16" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" s="8">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="8">
         <v>0.24805000000000002</v>
       </c>
-      <c r="E13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="E17" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D14" s="8">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="8">
         <v>0.25752999999999998</v>
       </c>
-      <c r="E14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="E18" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" s="8">
-        <v>0.11076</v>
-      </c>
-      <c r="E15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="D16" s="8">
-        <v>0.29315000000000002</v>
-      </c>
-      <c r="E16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17">
-        <v>0.4</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18">
-        <v>0.4</v>
-      </c>
-      <c r="E18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" s="1"/>
+      <c r="F18" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19">
-        <v>0.52500000000000002</v>
+        <v>71</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0.11076</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="1"/>
+        <v>38</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="8">
+        <v>0.29315000000000002</v>
+      </c>
+      <c r="E20" t="s">
         <v>38</v>
       </c>
-      <c r="B20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E20" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" s="1"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D21">
-        <v>0.52500000000000002</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
-      </c>
-      <c r="F21" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="F21" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D22">
-        <v>1.0880000000000001</v>
+        <v>130</v>
       </c>
       <c r="E22" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F22" s="1"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="D23">
-        <v>1.0880000000000001</v>
-      </c>
-      <c r="E23" t="s">
-        <v>65</v>
+        <v>215</v>
       </c>
       <c r="F23" s="1"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="D24">
-        <v>1.0880000000000001</v>
-      </c>
-      <c r="E24" t="s">
-        <v>65</v>
+        <v>265</v>
       </c>
       <c r="F24" s="1"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D25">
-        <v>1.0660000000000001</v>
-      </c>
-      <c r="E25" t="s">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="F25" s="1"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D26">
-        <v>1.0660000000000001</v>
-      </c>
-      <c r="E26" t="s">
-        <v>65</v>
+        <v>350</v>
       </c>
       <c r="F26" s="1"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="D27">
-        <v>1.0660000000000001</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>72</v>
+        <v>61</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="D28">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="E28" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="1"/>
+      <c r="F28" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>74</v>
+        <v>62</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="D29">
-        <v>3.1</v>
+        <v>40</v>
       </c>
       <c r="E29" t="s">
         <v>65</v>
       </c>
-      <c r="F29" s="1"/>
+      <c r="F29" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>73</v>
+        <v>104</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="D30">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="E30" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30" s="1"/>
+        <v>14</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>100</v>
+        <v>42</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>4.8274562E-2</v>
       </c>
       <c r="E31" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="F31" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>76</v>
+        <v>6</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="D32">
-        <v>130</v>
+        <v>0.03</v>
       </c>
       <c r="E32" t="s">
-        <v>77</v>
-      </c>
-      <c r="F32" s="1"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>78</v>
+        <v>56</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="D33">
-        <v>215</v>
-      </c>
-      <c r="F33" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E33" t="s">
+        <v>57</v>
+      </c>
+      <c r="F33" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>79</v>
+        <v>66</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="D34">
-        <v>265</v>
-      </c>
-      <c r="F34" s="1"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35">
-        <v>320</v>
-      </c>
-      <c r="F35" s="1"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36">
-        <v>350</v>
-      </c>
-      <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D37">
-        <v>2</v>
-      </c>
-      <c r="E37" t="s">
-        <v>95</v>
-      </c>
-      <c r="F37" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>90</v>
-      </c>
-      <c r="B38" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D38">
-        <v>30</v>
-      </c>
-      <c r="E38" t="s">
-        <v>95</v>
-      </c>
-      <c r="F38" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39">
-        <v>0.594322503</v>
-      </c>
-      <c r="E39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40">
-        <v>4.8274562E-2</v>
-      </c>
-      <c r="E40" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41">
-        <v>0.03</v>
-      </c>
-      <c r="E41" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D42">
-        <v>10</v>
-      </c>
-      <c r="E42" t="s">
-        <v>87</v>
-      </c>
-      <c r="F42" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" t="s">
-        <v>97</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D43">
         <v>0.1</v>
       </c>
     </row>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE3A243-80F5-44A1-8423-2282262088E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31BEA2C-D059-4771-930A-8FB854BC1DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="118">
   <si>
     <t>category</t>
   </si>
@@ -333,9 +333,6 @@
     <t>2040 sem price</t>
   </si>
   <si>
-    <t>mean wholesale price</t>
-  </si>
-  <si>
     <t>sem_price_2030</t>
   </si>
   <si>
@@ -373,6 +370,45 @@
   </si>
   <si>
     <t>hourly MAE assuming 2026 dynamic prices and LP1 load</t>
+  </si>
+  <si>
+    <t>2030 dynamic standing charge</t>
+  </si>
+  <si>
+    <t>2040 dynamic standing charge</t>
+  </si>
+  <si>
+    <t>2026 dynamic standing charge</t>
+  </si>
+  <si>
+    <t>dynamic_standing_charge_2026</t>
+  </si>
+  <si>
+    <t>dynamic_standing_charge_2030</t>
+  </si>
+  <si>
+    <t>dynamic_standing_charge_2040</t>
+  </si>
+  <si>
+    <t>sem_price_2026</t>
+  </si>
+  <si>
+    <t>2026 sem price</t>
+  </si>
+  <si>
+    <t>trend price at end of 2025</t>
+  </si>
+  <si>
+    <t>CU 2026 dynamic price cap</t>
+  </si>
+  <si>
+    <t>dynamic_cap</t>
+  </si>
+  <si>
+    <t>CRU cap in 2026/ Assumed to scale with sem trend price</t>
+  </si>
+  <si>
+    <t>trend wholesale price</t>
   </si>
 </sst>
 </file>
@@ -907,7 +943,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -975,10 +1011,10 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4">
         <v>0.13500000000000001</v>
@@ -989,10 +1025,10 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5">
         <v>0.09</v>
@@ -1003,10 +1039,10 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="D6">
         <v>0.13500000000000001</v>
@@ -1014,22 +1050,22 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D7">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1037,37 +1073,39 @@
         <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D8">
-        <v>0.2</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="F8" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.16838500000000001</v>
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9">
+        <v>0.15</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1075,262 +1113,270 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="8">
-        <v>7.2419999999999998E-2</v>
+        <v>91</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10">
+        <v>0.2</v>
       </c>
       <c r="E10" t="s">
         <v>38</v>
       </c>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>76</v>
+      <c r="A11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="D11" s="8">
-        <v>0.19167500000000001</v>
+        <v>0.16838500000000001</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
       </c>
+      <c r="F11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12">
-        <v>0.1981</v>
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="8">
+        <v>7.2419999999999998E-2</v>
       </c>
       <c r="E12" t="s">
         <v>38</v>
       </c>
-      <c r="F12" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13">
-        <v>8.5199999999999998E-2</v>
+      <c r="A13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.19167500000000001</v>
       </c>
       <c r="E13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>86</v>
+      <c r="A14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="D14">
-        <v>0.22550000000000001</v>
+        <v>0.1981</v>
       </c>
       <c r="E14" t="s">
         <v>38</v>
       </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="8">
-        <v>0.21791000000000002</v>
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15">
+        <v>8.5199999999999998E-2</v>
       </c>
       <c r="E15" t="s">
         <v>38</v>
       </c>
-      <c r="F15" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" s="8">
-        <v>9.3720000000000012E-2</v>
+      <c r="A16" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16">
+        <v>0.22550000000000001</v>
       </c>
       <c r="E16" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>79</v>
+      <c r="A17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="D17" s="8">
-        <v>0.24805000000000002</v>
+        <v>0.21791000000000002</v>
       </c>
       <c r="E17" t="s">
         <v>38</v>
       </c>
+      <c r="F17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>87</v>
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="D18" s="8">
-        <v>0.25752999999999998</v>
+        <v>9.3720000000000012E-2</v>
       </c>
       <c r="E18" t="s">
         <v>38</v>
       </c>
-      <c r="F18" t="s">
-        <v>83</v>
-      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>88</v>
+      <c r="A19" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="D19" s="8">
-        <v>0.11076</v>
+        <v>0.24805000000000002</v>
       </c>
       <c r="E19" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>89</v>
+      <c r="A20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="D20" s="8">
-        <v>0.29315000000000002</v>
+        <v>0.25752999999999998</v>
       </c>
       <c r="E20" t="s">
         <v>38</v>
       </c>
+      <c r="F20" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
+        <v>71</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0.11076</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22">
-        <v>130</v>
+      <c r="A22" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="8">
+        <v>0.29315000000000002</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="1"/>
+        <v>38</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="D23">
-        <v>215</v>
-      </c>
-      <c r="F23" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D24">
-        <v>265</v>
+        <v>130</v>
+      </c>
+      <c r="E24" t="s">
+        <v>47</v>
       </c>
       <c r="F24" s="1"/>
     </row>
@@ -1339,13 +1385,13 @@
         <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D25">
-        <v>320</v>
+        <v>215</v>
       </c>
       <c r="F25" s="1"/>
     </row>
@@ -1354,159 +1400,242 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D26">
-        <v>350</v>
+        <v>265</v>
       </c>
       <c r="F26" s="1"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D27">
-        <v>12</v>
-      </c>
-      <c r="E27" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D28">
-        <v>5</v>
-      </c>
-      <c r="E28" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" t="s">
-        <v>105</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="F28" s="1"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>64</v>
+        <v>107</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="D29">
-        <v>40</v>
-      </c>
-      <c r="E29" t="s">
-        <v>65</v>
-      </c>
-      <c r="F29" t="s">
-        <v>105</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="F29" s="1"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>13</v>
+        <v>105</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="D30">
-        <v>0.2</v>
-      </c>
-      <c r="E30" t="s">
-        <v>14</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="F30" s="1"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>8</v>
+        <v>106</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="D31">
-        <v>4.8274562E-2</v>
-      </c>
-      <c r="E31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" t="s">
-        <v>43</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32">
-        <v>0.03</v>
-      </c>
-      <c r="E32" t="s">
-        <v>17</v>
-      </c>
+      <c r="C32" s="7"/>
+      <c r="F32" s="1"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33">
-        <v>10</v>
-      </c>
-      <c r="E33" t="s">
-        <v>57</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
+      <c r="C33" s="7"/>
+      <c r="F33" s="1"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>102</v>
+      </c>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35">
+        <v>5</v>
+      </c>
+      <c r="E35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F35" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36">
+        <v>40</v>
+      </c>
+      <c r="E36" t="s">
+        <v>65</v>
+      </c>
+      <c r="F36" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>7</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B37" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37">
+        <v>0.2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38">
+        <v>4.8274562E-2</v>
+      </c>
+      <c r="E38" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39">
+        <v>0.03</v>
+      </c>
+      <c r="E39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D34">
+      <c r="D41">
         <v>0.1</v>
       </c>
     </row>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31BEA2C-D059-4771-930A-8FB854BC1DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE11832-0B16-4E89-9AC1-77F75C52A530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -943,7 +943,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -1486,69 +1486,98 @@
       <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C32" s="7"/>
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>102</v>
+      </c>
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C33" s="7"/>
-      <c r="F33" s="1"/>
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>65</v>
+      </c>
+      <c r="F33" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>101</v>
+        <v>62</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E34" t="s">
-        <v>102</v>
-      </c>
-      <c r="F34" s="1"/>
+        <v>65</v>
+      </c>
+      <c r="F34" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="E35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F35" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="D36">
-        <v>40</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E36" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="F36" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1556,16 +1585,16 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D37">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1573,19 +1602,19 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="D38">
-        <v>4.8274562E-2</v>
+        <v>10</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="F38" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1593,49 +1622,12 @@
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D39">
-        <v>0.03</v>
-      </c>
-      <c r="E39" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D40">
-        <v>10</v>
-      </c>
-      <c r="E40" t="s">
-        <v>57</v>
-      </c>
-      <c r="F40" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D41">
         <v>0.1</v>
       </c>
     </row>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE11832-0B16-4E89-9AC1-77F75C52A530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BBF324F-D5CE-4F23-8522-004479F0646A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="118">
   <si>
     <t>category</t>
   </si>
@@ -369,9 +369,6 @@
     <t>social factor</t>
   </si>
   <si>
-    <t>hourly MAE assuming 2026 dynamic prices and LP1 load</t>
-  </si>
-  <si>
     <t>2030 dynamic standing charge</t>
   </si>
   <si>
@@ -409,6 +406,9 @@
   </si>
   <si>
     <t>trend wholesale price</t>
+  </si>
+  <si>
+    <t>mean flex in lp2 is 14%</t>
   </si>
 </sst>
 </file>
@@ -512,7 +512,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -535,6 +535,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1053,10 +1054,10 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>114</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>115</v>
       </c>
       <c r="D7">
         <v>0.5</v>
@@ -1065,7 +1066,7 @@
         <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1073,10 +1074,10 @@
         <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D8">
         <v>9.2999999999999999E-2</v>
@@ -1085,7 +1086,7 @@
         <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1105,7 +1106,7 @@
         <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1445,10 +1446,10 @@
         <v>37</v>
       </c>
       <c r="B29" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>108</v>
       </c>
       <c r="D29">
         <v>265</v>
@@ -1460,10 +1461,10 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D30">
         <v>320</v>
@@ -1475,10 +1476,10 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D31">
         <v>350</v>
@@ -1513,14 +1514,11 @@
       <c r="C33" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D33">
-        <v>5</v>
+      <c r="D33" s="14">
+        <v>0.02</v>
       </c>
       <c r="E33" t="s">
         <v>65</v>
-      </c>
-      <c r="F33" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1533,14 +1531,14 @@
       <c r="C34" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D34">
-        <v>40</v>
+      <c r="D34" s="14">
+        <v>0.28000000000000003</v>
       </c>
       <c r="E34" t="s">
         <v>65</v>
       </c>
       <c r="F34" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BBF324F-D5CE-4F23-8522-004479F0646A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2D8718-6CA4-4EC2-B347-AC6E4412A657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="117">
   <si>
     <t>category</t>
   </si>
@@ -246,15 +246,6 @@
     <t>maximum household hourly flexibility</t>
   </si>
   <si>
-    <t>min_flex</t>
-  </si>
-  <si>
-    <t>max_flex</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
     <t>max risk aversion</t>
   </si>
   <si>
@@ -409,6 +400,12 @@
   </si>
   <si>
     <t>mean flex in lp2 is 14%</t>
+  </si>
+  <si>
+    <t>flex_sigma.</t>
+  </si>
+  <si>
+    <t>flex_scale.</t>
   </si>
 </sst>
 </file>
@@ -512,7 +509,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -535,7 +532,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="2" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1012,10 +1008,10 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D4">
         <v>0.13500000000000001</v>
@@ -1026,10 +1022,10 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D5">
         <v>0.09</v>
@@ -1040,10 +1036,10 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D6">
         <v>0.13500000000000001</v>
@@ -1054,10 +1050,10 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D7">
         <v>0.5</v>
@@ -1066,7 +1062,7 @@
         <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1074,10 +1070,10 @@
         <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D8">
         <v>9.2999999999999999E-2</v>
@@ -1086,7 +1082,7 @@
         <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1094,10 +1090,10 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D9">
         <v>0.15</v>
@@ -1106,7 +1102,7 @@
         <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1114,10 +1110,10 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D10">
         <v>0.2</v>
@@ -1132,10 +1128,10 @@
         <v>37</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D11" s="8">
         <v>0.16838500000000001</v>
@@ -1144,7 +1140,7 @@
         <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1152,10 +1148,10 @@
         <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D12" s="8">
         <v>7.2419999999999998E-2</v>
@@ -1169,10 +1165,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D13" s="8">
         <v>0.19167500000000001</v>
@@ -1186,10 +1182,10 @@
         <v>37</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D14">
         <v>0.1981</v>
@@ -1198,7 +1194,7 @@
         <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1206,10 +1202,10 @@
         <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D15">
         <v>8.5199999999999998E-2</v>
@@ -1223,10 +1219,10 @@
         <v>37</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D16">
         <v>0.22550000000000001</v>
@@ -1240,10 +1236,10 @@
         <v>37</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D17" s="8">
         <v>0.21791000000000002</v>
@@ -1252,7 +1248,7 @@
         <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1260,10 +1256,10 @@
         <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D18" s="8">
         <v>9.3720000000000012E-2</v>
@@ -1277,10 +1273,10 @@
         <v>37</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D19" s="8">
         <v>0.24805000000000002</v>
@@ -1294,10 +1290,10 @@
         <v>37</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D20" s="8">
         <v>0.25752999999999998</v>
@@ -1306,7 +1302,7 @@
         <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1314,10 +1310,10 @@
         <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D21" s="8">
         <v>0.11076</v>
@@ -1331,10 +1327,10 @@
         <v>37</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D22" s="8">
         <v>0.29315000000000002</v>
@@ -1348,10 +1344,10 @@
         <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -1360,7 +1356,7 @@
         <v>44</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1446,10 +1442,10 @@
         <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D29">
         <v>265</v>
@@ -1461,10 +1457,10 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D30">
         <v>320</v>
@@ -1476,10 +1472,10 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D31">
         <v>350</v>
@@ -1491,16 +1487,16 @@
         <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D32">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F32" s="1"/>
     </row>
@@ -1512,13 +1508,10 @@
         <v>61</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D33" s="14">
-        <v>0.02</v>
-      </c>
-      <c r="E33" t="s">
-        <v>65</v>
+        <v>115</v>
+      </c>
+      <c r="D33">
+        <v>2.5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1529,16 +1522,13 @@
         <v>62</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="14">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E34" t="s">
-        <v>65</v>
+        <v>116</v>
+      </c>
+      <c r="D34">
+        <v>13</v>
       </c>
       <c r="F34" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1546,7 +1536,7 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>13</v>
@@ -1620,10 +1610,10 @@
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D39">
         <v>0.1</v>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2D8718-6CA4-4EC2-B347-AC6E4412A657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3315D9ED-F1BE-491C-942B-8BCEBF1FDAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1525,7 +1525,7 @@
         <v>116</v>
       </c>
       <c r="D34">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="F34" t="s">
         <v>114</v>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3315D9ED-F1BE-491C-942B-8BCEBF1FDAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8ED06A0-755F-49F1-8C79-3C9E0F70677D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="131">
   <si>
     <t>category</t>
   </si>
@@ -246,9 +246,6 @@
     <t>maximum household hourly flexibility</t>
   </si>
   <si>
-    <t>max risk aversion</t>
-  </si>
-  <si>
     <t>theta.</t>
   </si>
   <si>
@@ -406,6 +403,51 @@
   </si>
   <si>
     <t>flex_scale.</t>
+  </si>
+  <si>
+    <t>prospect theory</t>
+  </si>
+  <si>
+    <t>pt_alpha</t>
+  </si>
+  <si>
+    <t>pt_beta</t>
+  </si>
+  <si>
+    <t>alpha parameter</t>
+  </si>
+  <si>
+    <t>beta parameter</t>
+  </si>
+  <si>
+    <t>loss averse probability weights</t>
+  </si>
+  <si>
+    <t>confidence in flexiblity  tou</t>
+  </si>
+  <si>
+    <t>confidence in flexiblity outcome dynamic</t>
+  </si>
+  <si>
+    <t>pt_prob_weight_gains</t>
+  </si>
+  <si>
+    <t>pt_certainty_flex_tou</t>
+  </si>
+  <si>
+    <t>pt_certainty_flex_det</t>
+  </si>
+  <si>
+    <t>pain parameter</t>
+  </si>
+  <si>
+    <t>pt_loss_aversion</t>
+  </si>
+  <si>
+    <t>pt_prob_weight_losses</t>
+  </si>
+  <si>
+    <t>max tech adoption barrier</t>
   </si>
 </sst>
 </file>
@@ -415,7 +457,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,8 +500,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -474,6 +523,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -504,12 +559,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -532,8 +588,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="40% - Accent4" xfId="3" builtinId="43"/>
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -940,7 +998,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -1008,10 +1066,10 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4">
         <v>0.13500000000000001</v>
@@ -1022,10 +1080,10 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5">
         <v>0.09</v>
@@ -1036,10 +1094,10 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="D6">
         <v>0.13500000000000001</v>
@@ -1050,10 +1108,10 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="D7">
         <v>0.5</v>
@@ -1062,7 +1120,7 @@
         <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1070,10 +1128,10 @@
         <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8">
         <v>9.2999999999999999E-2</v>
@@ -1082,7 +1140,7 @@
         <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1090,10 +1148,10 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D9">
         <v>0.15</v>
@@ -1102,7 +1160,7 @@
         <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1110,10 +1168,10 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D10">
         <v>0.2</v>
@@ -1128,10 +1186,10 @@
         <v>37</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="D11" s="8">
         <v>0.16838500000000001</v>
@@ -1140,7 +1198,7 @@
         <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1148,10 +1206,10 @@
         <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" s="8">
         <v>7.2419999999999998E-2</v>
@@ -1165,10 +1223,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" s="8">
         <v>0.19167500000000001</v>
@@ -1182,10 +1240,10 @@
         <v>37</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D14">
         <v>0.1981</v>
@@ -1194,7 +1252,7 @@
         <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1202,10 +1260,10 @@
         <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15">
         <v>8.5199999999999998E-2</v>
@@ -1219,10 +1277,10 @@
         <v>37</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D16">
         <v>0.22550000000000001</v>
@@ -1236,10 +1294,10 @@
         <v>37</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D17" s="8">
         <v>0.21791000000000002</v>
@@ -1248,7 +1306,7 @@
         <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1256,10 +1314,10 @@
         <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D18" s="8">
         <v>9.3720000000000012E-2</v>
@@ -1273,10 +1331,10 @@
         <v>37</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" s="8">
         <v>0.24805000000000002</v>
@@ -1290,10 +1348,10 @@
         <v>37</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D20" s="8">
         <v>0.25752999999999998</v>
@@ -1302,7 +1360,7 @@
         <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1310,10 +1368,10 @@
         <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D21" s="8">
         <v>0.11076</v>
@@ -1327,10 +1385,10 @@
         <v>37</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D22" s="8">
         <v>0.29315000000000002</v>
@@ -1344,10 +1402,10 @@
         <v>37</v>
       </c>
       <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>66</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -1356,7 +1414,7 @@
         <v>44</v>
       </c>
       <c r="F23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1442,10 +1500,10 @@
         <v>37</v>
       </c>
       <c r="B29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>104</v>
       </c>
       <c r="D29">
         <v>265</v>
@@ -1457,10 +1515,10 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D30">
         <v>320</v>
@@ -1472,10 +1530,10 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D31">
         <v>350</v>
@@ -1487,136 +1545,241 @@
         <v>60</v>
       </c>
       <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="D32">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>117</v>
       </c>
       <c r="D33">
-        <v>2.5</v>
-      </c>
+        <v>0.88</v>
+      </c>
+      <c r="F33" s="1"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>118</v>
       </c>
       <c r="D34">
-        <v>16.5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>114</v>
-      </c>
+        <v>0.88</v>
+      </c>
+      <c r="F34" s="1"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>13</v>
+        <v>127</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="D35">
-        <v>0.2</v>
-      </c>
-      <c r="E35" t="s">
-        <v>14</v>
-      </c>
+        <v>2.25</v>
+      </c>
+      <c r="F35" s="1"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>8</v>
+        <v>121</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>124</v>
       </c>
       <c r="D36">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="E36" t="s">
-        <v>14</v>
-      </c>
-      <c r="F36" t="s">
-        <v>43</v>
-      </c>
+        <v>0.61</v>
+      </c>
+      <c r="F36" s="1"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>16</v>
+        <v>121</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="D37">
-        <v>0.03</v>
-      </c>
-      <c r="E37" t="s">
-        <v>17</v>
-      </c>
+        <v>0.69</v>
+      </c>
+      <c r="F37" s="1"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>58</v>
+        <v>122</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="D38">
-        <v>10</v>
-      </c>
-      <c r="E38" t="s">
-        <v>57</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="F38" s="1"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39">
+        <v>0.7</v>
+      </c>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>7</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D40">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D41">
+        <v>16.5</v>
+      </c>
+      <c r="F41" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42">
+        <v>0.2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44">
+        <v>0.03</v>
+      </c>
+      <c r="E44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45">
+        <v>10</v>
+      </c>
+      <c r="E45" t="s">
+        <v>57</v>
+      </c>
+      <c r="F45" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D39">
-        <v>0.1</v>
+      <c r="D46">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8ED06A0-755F-49F1-8C79-3C9E0F70677D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06A29E7-2BF4-4EB8-8206-43FFA14B1558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1688,7 +1688,7 @@
         <v>115</v>
       </c>
       <c r="D41">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="F41" t="s">
         <v>113</v>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06A29E7-2BF4-4EB8-8206-43FFA14B1558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306D093A-DE37-48C4-B535-5BAAA85DFA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -396,15 +396,6 @@
     <t>trend wholesale price</t>
   </si>
   <si>
-    <t>mean flex in lp2 is 14%</t>
-  </si>
-  <si>
-    <t>flex_sigma.</t>
-  </si>
-  <si>
-    <t>flex_scale.</t>
-  </si>
-  <si>
     <t>prospect theory</t>
   </si>
   <si>
@@ -448,6 +439,15 @@
   </si>
   <si>
     <t>max tech adoption barrier</t>
+  </si>
+  <si>
+    <t>flex_alpha.</t>
+  </si>
+  <si>
+    <t>flex_beta.</t>
+  </si>
+  <si>
+    <t>beta &gt; alpha left skew</t>
   </si>
 </sst>
 </file>
@@ -1560,13 +1560,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" t="s">
         <v>116</v>
       </c>
-      <c r="B33" t="s">
-        <v>119</v>
-      </c>
       <c r="C33" s="14" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D33">
         <v>0.88</v>
@@ -1575,13 +1575,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D34">
         <v>0.88</v>
@@ -1590,13 +1590,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D35">
         <v>2.25</v>
@@ -1605,13 +1605,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B36" t="s">
+        <v>118</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>121</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>124</v>
       </c>
       <c r="D36">
         <v>0.61</v>
@@ -1620,13 +1620,13 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D37">
         <v>0.69</v>
@@ -1635,13 +1635,13 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B38" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="14" t="s">
         <v>122</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>125</v>
       </c>
       <c r="D38">
         <v>0.8</v>
@@ -1650,13 +1650,13 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B39" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" s="14" t="s">
         <v>123</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>126</v>
       </c>
       <c r="D39">
         <v>0.7</v>
@@ -1671,10 +1671,10 @@
         <v>61</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="D40">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -1685,13 +1685,13 @@
         <v>62</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D41">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -1773,7 +1773,7 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>63</v>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306D093A-DE37-48C4-B535-5BAAA85DFA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA4C6CE-A7CA-4C8E-902C-7B4BF2D9C69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -366,15 +366,6 @@
     <t>2026 dynamic standing charge</t>
   </si>
   <si>
-    <t>dynamic_standing_charge_2026</t>
-  </si>
-  <si>
-    <t>dynamic_standing_charge_2030</t>
-  </si>
-  <si>
-    <t>dynamic_standing_charge_2040</t>
-  </si>
-  <si>
     <t>sem_price_2026</t>
   </si>
   <si>
@@ -448,6 +439,15 @@
   </si>
   <si>
     <t>beta &gt; alpha left skew</t>
+  </si>
+  <si>
+    <t>dep_standing_charge_premium_2026</t>
+  </si>
+  <si>
+    <t>dep_standing_charge_premium_2030</t>
+  </si>
+  <si>
+    <t>dep_standing_charge_premium_2040</t>
   </si>
 </sst>
 </file>
@@ -1108,10 +1108,10 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D7">
         <v>0.5</v>
@@ -1120,7 +1120,7 @@
         <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1128,10 +1128,10 @@
         <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D8">
         <v>9.2999999999999999E-2</v>
@@ -1140,7 +1140,7 @@
         <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1160,7 +1160,7 @@
         <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1503,10 +1503,10 @@
         <v>102</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="D29">
-        <v>265</v>
+        <v>75</v>
       </c>
       <c r="F29" s="1"/>
     </row>
@@ -1518,10 +1518,10 @@
         <v>100</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="D30">
-        <v>320</v>
+        <v>75</v>
       </c>
       <c r="F30" s="1"/>
     </row>
@@ -1533,10 +1533,10 @@
         <v>101</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="D31">
-        <v>350</v>
+        <v>75</v>
       </c>
       <c r="F31" s="1"/>
     </row>
@@ -1560,13 +1560,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" t="s">
         <v>113</v>
       </c>
-      <c r="B33" t="s">
-        <v>116</v>
-      </c>
       <c r="C33" s="14" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D33">
         <v>0.88</v>
@@ -1575,13 +1575,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D34">
         <v>0.88</v>
@@ -1590,13 +1590,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D35">
         <v>2.25</v>
@@ -1605,13 +1605,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>118</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>121</v>
       </c>
       <c r="D36">
         <v>0.61</v>
@@ -1620,13 +1620,13 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D37">
         <v>0.69</v>
@@ -1635,13 +1635,13 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
+        <v>116</v>
+      </c>
+      <c r="C38" s="14" t="s">
         <v>119</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>122</v>
       </c>
       <c r="D38">
         <v>0.8</v>
@@ -1650,13 +1650,13 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="14" t="s">
         <v>120</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>123</v>
       </c>
       <c r="D39">
         <v>0.7</v>
@@ -1671,7 +1671,7 @@
         <v>61</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -1685,13 +1685,13 @@
         <v>62</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D41">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -1773,7 +1773,7 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>63</v>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA4C6CE-A7CA-4C8E-902C-7B4BF2D9C69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB69CE5E-586C-48B2-9B5A-6F95547A3E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1722,7 +1722,7 @@
         <v>8</v>
       </c>
       <c r="D43">
-        <v>5.0000000000000001E-3</v>
+        <v>0.03</v>
       </c>
       <c r="E43" t="s">
         <v>14</v>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\depmicrosimr\inst\ext_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB69CE5E-586C-48B2-9B5A-6F95547A3E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB320F55-8999-4D73-B5D7-7FAF7F113713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="117">
   <si>
     <t>category</t>
   </si>
@@ -81,64 +81,7 @@
     <t>nu.</t>
   </si>
   <si>
-    <t>macro calibration</t>
-  </si>
-  <si>
-    <t>hpmicromsimr scenario_params</t>
-  </si>
-  <si>
     <t>r.</t>
-  </si>
-  <si>
-    <t>rename to r.</t>
-  </si>
-  <si>
-    <t>WEM</t>
-  </si>
-  <si>
-    <t>With Additional Measures</t>
-  </si>
-  <si>
-    <t>WAM</t>
-  </si>
-  <si>
-    <t>With Existing Measures</t>
-  </si>
-  <si>
-    <t>CAP</t>
-  </si>
-  <si>
-    <t>Climate Action Plan 2024</t>
-  </si>
-  <si>
-    <t>DWIT</t>
-  </si>
-  <si>
-    <t>"do whatever it takes"</t>
-  </si>
-  <si>
-    <t>81.5k heat pump retrofits by 2019-2030</t>
-  </si>
-  <si>
-    <t>143k heat pump retrofits 2019-2030 120k DERs by 2030</t>
-  </si>
-  <si>
-    <t>2025 45k heat pumps retrofits, efficiency grants maintained to 2040 carbon taxes as planned</t>
-  </si>
-  <si>
-    <t>approximately 240k heat pump retrofits by 2030</t>
-  </si>
-  <si>
-    <t>hit both emissions and EED sectoral target</t>
-  </si>
-  <si>
-    <t>(1) carbon price 200/tCO2 in 2030 (2) relax HLI rule to 3.0 in 2028 (3) ban new boilers in 2028 (4) 65% immediate increase in grant supports (5) warmers home deeper retrofits, cost cap at 50k</t>
-  </si>
-  <si>
-    <t>Assumed measures: (1) 60% immediate increase in grants (2) 50% increase in warmer homes cost effective cap to 45k and strict B2 (3) relax HLI heat pump rule to 2.8 in 3031 (4) oil boiler ban in 3031 (4) effective carbon price is doubled to 200t/CO2 in 2030 and 400t/CO2 in 2040</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (1) upgrade grants increased by 35% (2) warming homes cost cap increased to 45k and strict B2 in mide 2028. All other measures maintained to 2041</t>
   </si>
   <si>
     <t>introduction time of dynamic pricing</t>
@@ -183,12 +126,6 @@
     <t>effective date for now (smart meter rollout)</t>
   </si>
   <si>
-    <t>inertia param</t>
-  </si>
-  <si>
-    <t>heterogeneous</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -234,18 +171,9 @@
     <t>s.</t>
   </si>
   <si>
-    <t>handling negative prices</t>
-  </si>
-  <si>
     <t>technical</t>
   </si>
   <si>
-    <t>minimum household hourly flexibility</t>
-  </si>
-  <si>
-    <t>maximum household hourly flexibility</t>
-  </si>
-  <si>
     <t>theta.</t>
   </si>
   <si>
@@ -448,6 +376,36 @@
   </si>
   <si>
     <t>dep_standing_charge_premium_2040</t>
+  </si>
+  <si>
+    <t>inertia param (p_rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta distribution </t>
+  </si>
+  <si>
+    <t>BASE</t>
+  </si>
+  <si>
+    <t>Base scenario</t>
+  </si>
+  <si>
+    <t>More or less the current situation except that the standing charge for all tariff plans are assumed to be the same</t>
+  </si>
+  <si>
+    <t>depmicromsimr scenario description</t>
+  </si>
+  <si>
+    <t>not used</t>
+  </si>
+  <si>
+    <t>estimate from CRU switching data</t>
+  </si>
+  <si>
+    <t>used to handle negative SEM prices</t>
+  </si>
+  <si>
+    <t>not used, social norm model used instead</t>
   </si>
 </sst>
 </file>
@@ -565,16 +523,13 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -589,6 +544,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="40% - Accent4" xfId="3" builtinId="43"/>
@@ -906,10 +865,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2536B528-ACE0-4AEE-80FE-2144BA4A4410}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="26.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="37.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="43.33203125" style="2" customWidth="1"/>
     <col min="4" max="4" width="33.21875" style="2" customWidth="1"/>
@@ -917,79 +876,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A1" s="14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="A3" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1031,13 +946,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>36</v>
+        <v>15</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D2">
         <v>2026.5</v>
@@ -1046,30 +961,30 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>40</v>
+        <v>20</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="D3">
         <v>2021</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>92</v>
+        <v>66</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="D4">
         <v>0.13500000000000001</v>
@@ -1077,13 +992,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>93</v>
+        <v>67</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="D5">
         <v>0.09</v>
@@ -1091,13 +1006,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>95</v>
+        <v>70</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="D6">
         <v>0.13500000000000001</v>
@@ -1105,345 +1020,345 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>107</v>
+        <v>82</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="D7">
         <v>0.5</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>103</v>
+        <v>80</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="D8">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>88</v>
+        <v>62</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="D9">
         <v>0.15</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>89</v>
+        <v>63</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="D10">
         <v>0.2</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="8">
+      <c r="A11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="7">
         <v>0.16838500000000001</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="8">
+        <v>43</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="7">
         <v>7.2419999999999998E-2</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="8">
+      <c r="A13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="7">
         <v>0.19167500000000001</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>80</v>
+      <c r="A14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="D14">
         <v>0.1981</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>81</v>
+        <v>43</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="D15">
         <v>8.5199999999999998E-2</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>82</v>
+      <c r="A16" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="D16">
         <v>0.22550000000000001</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="8">
+      <c r="A17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="7">
         <v>0.21791000000000002</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="8">
+        <v>43</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="7">
         <v>9.3720000000000012E-2</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="8">
+      <c r="A19" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="7">
         <v>0.24805000000000002</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" s="8">
+      <c r="A20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="7">
         <v>0.25752999999999998</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="8">
+        <v>43</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="7">
         <v>0.11076</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" s="8">
+      <c r="A22" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="7">
         <v>0.29315000000000002</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>65</v>
+        <v>40</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>46</v>
+        <v>24</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D24">
         <v>130</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F24" s="1"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>48</v>
+        <v>31</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="D25">
         <v>215</v>
@@ -1452,13 +1367,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>49</v>
+        <v>32</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="D26">
         <v>265</v>
@@ -1467,13 +1382,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>50</v>
+        <v>33</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="D27">
         <v>320</v>
@@ -1482,13 +1397,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>51</v>
+        <v>34</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="D28">
         <v>350</v>
@@ -1497,169 +1412,190 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>128</v>
+        <v>78</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="D29">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F29" s="1"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>129</v>
+        <v>76</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D30">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F30" s="1"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>130</v>
+        <v>77</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="D31">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>97</v>
+        <v>72</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="D32">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>111</v>
+        <v>89</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="D33">
         <v>0.88</v>
       </c>
+      <c r="E33" t="s">
+        <v>86</v>
+      </c>
       <c r="F33" s="1"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>112</v>
+        <v>90</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>88</v>
       </c>
       <c r="D34">
         <v>0.88</v>
       </c>
+      <c r="E34" t="s">
+        <v>86</v>
+      </c>
       <c r="F34" s="1"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>121</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>122</v>
+        <v>97</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="D35">
         <v>2.25</v>
       </c>
+      <c r="E35" t="s">
+        <v>86</v>
+      </c>
       <c r="F35" s="1"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>118</v>
+        <v>91</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>94</v>
       </c>
       <c r="D36">
         <v>0.61</v>
       </c>
+      <c r="E36" t="s">
+        <v>86</v>
+      </c>
       <c r="F36" s="1"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>115</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>123</v>
+        <v>91</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="D37">
         <v>0.69</v>
       </c>
+      <c r="E37" t="s">
+        <v>86</v>
+      </c>
       <c r="F37" s="1"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>119</v>
+        <v>92</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>95</v>
       </c>
       <c r="D38">
         <v>0.8</v>
       </c>
+      <c r="E38" t="s">
+        <v>86</v>
+      </c>
       <c r="F38" s="1"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>117</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>120</v>
+        <v>93</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>96</v>
       </c>
       <c r="D39">
         <v>0.7</v>
+      </c>
+      <c r="E39" t="s">
+        <v>86</v>
       </c>
       <c r="F39" s="1"/>
     </row>
@@ -1668,10 +1604,10 @@
         <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -1682,16 +1618,16 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="D41">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -1699,7 +1635,7 @@
         <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>13</v>
@@ -1708,7 +1644,7 @@
         <v>0.2</v>
       </c>
       <c r="E42" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1716,7 +1652,7 @@
         <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>8</v>
@@ -1725,10 +1661,7 @@
         <v>0.03</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1739,13 +1672,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D44">
         <v>0.03</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1753,19 +1686,19 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="D45">
         <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="F45" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -1773,13 +1706,16 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D46">
         <v>0</v>
+      </c>
+      <c r="E46" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/inst/ext_data/scenario_parameters.xlsx
+++ b/inst/ext_data/scenario_parameters.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB320F55-8999-4D73-B5D7-7FAF7F113713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="7" r:id="rId1"/>
@@ -544,7 +544,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
